--- a/Catch models/cinfo_macarellus_cmsy.xlsx
+++ b/Catch models/cinfo_macarellus_cmsy.xlsx
@@ -807,7 +807,7 @@
         <v>1989</v>
       </c>
       <c r="G2">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -849,22 +849,22 @@
         <v>1989</v>
       </c>
       <c r="U2">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V2">
         <v>1989</v>
       </c>
       <c r="W2">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF2" t="s">
         <v>59</v>
       </c>
       <c r="AG2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AH2">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AI2">
         <v>0.7</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="AN2">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AO2">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AP2" t="s">
         <v>60</v>
@@ -905,7 +905,7 @@
         <v>1989</v>
       </c>
       <c r="G3">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H3" t="s">
         <v>49</v>
@@ -947,13 +947,13 @@
         <v>1989</v>
       </c>
       <c r="U3">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V3">
         <v>1989</v>
       </c>
       <c r="W3">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF3" t="s">
         <v>59</v>
@@ -962,7 +962,7 @@
         <v>0.05</v>
       </c>
       <c r="AH3">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="AI3">
         <v>0.7</v>
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="AN3">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AO3">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AP3" t="s">
         <v>60</v>
@@ -1003,7 +1003,7 @@
         <v>1989</v>
       </c>
       <c r="G4">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H4" t="s">
         <v>49</v>
@@ -1045,22 +1045,22 @@
         <v>1989</v>
       </c>
       <c r="U4">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V4">
         <v>1989</v>
       </c>
       <c r="W4">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF4" t="s">
         <v>59</v>
       </c>
       <c r="AG4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AH4">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AI4">
         <v>0.7</v>
@@ -1069,10 +1069,10 @@
         <v>1</v>
       </c>
       <c r="AN4">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AO4">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AP4" t="s">
         <v>60</v>
@@ -1101,7 +1101,7 @@
         <v>1989</v>
       </c>
       <c r="G5">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H5" t="s">
         <v>49</v>
@@ -1143,13 +1143,13 @@
         <v>1989</v>
       </c>
       <c r="U5">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V5">
         <v>1989</v>
       </c>
       <c r="W5">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF5" t="s">
         <v>59</v>
@@ -1167,10 +1167,10 @@
         <v>1</v>
       </c>
       <c r="AN5">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AO5">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AP5" t="s">
         <v>60</v>
@@ -1199,7 +1199,7 @@
         <v>1989</v>
       </c>
       <c r="G6">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H6" t="s">
         <v>49</v>
@@ -1241,22 +1241,22 @@
         <v>1989</v>
       </c>
       <c r="U6">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V6">
         <v>1989</v>
       </c>
       <c r="W6">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF6" t="s">
         <v>59</v>
       </c>
       <c r="AG6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AH6">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AI6">
         <v>0.7</v>
@@ -1265,10 +1265,10 @@
         <v>1</v>
       </c>
       <c r="AN6">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="AO6">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="AP6" t="s">
         <v>60</v>
@@ -1297,7 +1297,7 @@
         <v>1989</v>
       </c>
       <c r="G7">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H7" t="s">
         <v>49</v>
@@ -1339,13 +1339,13 @@
         <v>1989</v>
       </c>
       <c r="U7">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V7">
         <v>1989</v>
       </c>
       <c r="W7">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF7" t="s">
         <v>59</v>
@@ -1354,7 +1354,7 @@
         <v>0.05</v>
       </c>
       <c r="AH7">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="AI7">
         <v>0.7</v>
@@ -1363,10 +1363,10 @@
         <v>1</v>
       </c>
       <c r="AN7">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="AO7">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="AP7" t="s">
         <v>60</v>
@@ -1395,7 +1395,7 @@
         <v>1989</v>
       </c>
       <c r="G8">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H8" t="s">
         <v>49</v>
@@ -1437,22 +1437,22 @@
         <v>1989</v>
       </c>
       <c r="U8">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V8">
         <v>1989</v>
       </c>
       <c r="W8">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF8" t="s">
         <v>59</v>
       </c>
       <c r="AG8">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AH8">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AI8">
         <v>0.7</v>
@@ -1461,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="AN8">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="AO8">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="AP8" t="s">
         <v>60</v>
@@ -1493,7 +1493,7 @@
         <v>1989</v>
       </c>
       <c r="G9">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H9" t="s">
         <v>49</v>
@@ -1535,13 +1535,13 @@
         <v>1989</v>
       </c>
       <c r="U9">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V9">
         <v>1989</v>
       </c>
       <c r="W9">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF9" t="s">
         <v>59</v>
@@ -1559,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="AN9">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="AO9">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="AP9" t="s">
         <v>60</v>
@@ -1591,7 +1591,7 @@
         <v>1989</v>
       </c>
       <c r="G10">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H10" t="s">
         <v>49</v>
@@ -1633,22 +1633,22 @@
         <v>1989</v>
       </c>
       <c r="U10">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V10">
         <v>1989</v>
       </c>
       <c r="W10">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF10" t="s">
         <v>59</v>
       </c>
       <c r="AG10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AH10">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AI10">
         <v>0.7</v>
@@ -1689,7 +1689,7 @@
         <v>1989</v>
       </c>
       <c r="G11">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H11" t="s">
         <v>49</v>
@@ -1731,13 +1731,13 @@
         <v>1989</v>
       </c>
       <c r="U11">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V11">
         <v>1989</v>
       </c>
       <c r="W11">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF11" t="s">
         <v>59</v>
@@ -1746,7 +1746,7 @@
         <v>0.05</v>
       </c>
       <c r="AH11">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="AI11">
         <v>0.7</v>
@@ -1787,7 +1787,7 @@
         <v>1989</v>
       </c>
       <c r="G12">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
@@ -1829,22 +1829,22 @@
         <v>1989</v>
       </c>
       <c r="U12">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V12">
         <v>1989</v>
       </c>
       <c r="W12">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF12" t="s">
         <v>59</v>
       </c>
       <c r="AG12">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AH12">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AI12">
         <v>0.7</v>
@@ -1885,7 +1885,7 @@
         <v>1989</v>
       </c>
       <c r="G13">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H13" t="s">
         <v>49</v>
@@ -1927,13 +1927,13 @@
         <v>1989</v>
       </c>
       <c r="U13">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V13">
         <v>1989</v>
       </c>
       <c r="W13">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF13" t="s">
         <v>59</v>
@@ -1983,7 +1983,7 @@
         <v>1989</v>
       </c>
       <c r="G14">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H14" t="s">
         <v>49</v>
@@ -2025,22 +2025,22 @@
         <v>1989</v>
       </c>
       <c r="U14">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V14">
         <v>1989</v>
       </c>
       <c r="W14">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF14" t="s">
         <v>59</v>
       </c>
       <c r="AG14">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AH14">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="AI14">
         <v>0.7</v>
@@ -2081,7 +2081,7 @@
         <v>1989</v>
       </c>
       <c r="G15">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H15" t="s">
         <v>49</v>
@@ -2123,13 +2123,13 @@
         <v>1989</v>
       </c>
       <c r="U15">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V15">
         <v>1989</v>
       </c>
       <c r="W15">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF15" t="s">
         <v>59</v>
@@ -2138,7 +2138,7 @@
         <v>0.05</v>
       </c>
       <c r="AH15">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="AI15">
         <v>0.7</v>
@@ -2179,7 +2179,7 @@
         <v>1989</v>
       </c>
       <c r="G16">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H16" t="s">
         <v>49</v>
@@ -2221,22 +2221,22 @@
         <v>1989</v>
       </c>
       <c r="U16">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V16">
         <v>1989</v>
       </c>
       <c r="W16">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF16" t="s">
         <v>59</v>
       </c>
       <c r="AG16">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AH16">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AI16">
         <v>0.7</v>
@@ -2277,7 +2277,7 @@
         <v>1989</v>
       </c>
       <c r="G17">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="H17" t="s">
         <v>49</v>
@@ -2319,13 +2319,13 @@
         <v>1989</v>
       </c>
       <c r="U17">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="V17">
         <v>1989</v>
       </c>
       <c r="W17">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="AF17" t="s">
         <v>59</v>

--- a/Catch models/cinfo_macarellus_cmsy.xlsx
+++ b/Catch models/cinfo_macarellus_cmsy.xlsx
@@ -807,7 +807,7 @@
         <v>1989</v>
       </c>
       <c r="G2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
@@ -849,13 +849,13 @@
         <v>1989</v>
       </c>
       <c r="U2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V2">
         <v>1989</v>
       </c>
       <c r="W2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF2" t="s">
         <v>59</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="AN2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AO2">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AP2" t="s">
         <v>60</v>
@@ -905,7 +905,7 @@
         <v>1989</v>
       </c>
       <c r="G3">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H3" t="s">
         <v>49</v>
@@ -947,13 +947,13 @@
         <v>1989</v>
       </c>
       <c r="U3">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V3">
         <v>1989</v>
       </c>
       <c r="W3">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF3" t="s">
         <v>59</v>
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="AN3">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AO3">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AP3" t="s">
         <v>60</v>
@@ -1003,7 +1003,7 @@
         <v>1989</v>
       </c>
       <c r="G4">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H4" t="s">
         <v>49</v>
@@ -1045,13 +1045,13 @@
         <v>1989</v>
       </c>
       <c r="U4">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V4">
         <v>1989</v>
       </c>
       <c r="W4">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF4" t="s">
         <v>59</v>
@@ -1069,10 +1069,10 @@
         <v>1</v>
       </c>
       <c r="AN4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AO4">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AP4" t="s">
         <v>60</v>
@@ -1101,7 +1101,7 @@
         <v>1989</v>
       </c>
       <c r="G5">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H5" t="s">
         <v>49</v>
@@ -1143,13 +1143,13 @@
         <v>1989</v>
       </c>
       <c r="U5">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V5">
         <v>1989</v>
       </c>
       <c r="W5">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF5" t="s">
         <v>59</v>
@@ -1167,10 +1167,10 @@
         <v>1</v>
       </c>
       <c r="AN5">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AO5">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AP5" t="s">
         <v>60</v>
@@ -1199,7 +1199,7 @@
         <v>1989</v>
       </c>
       <c r="G6">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H6" t="s">
         <v>49</v>
@@ -1241,13 +1241,13 @@
         <v>1989</v>
       </c>
       <c r="U6">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V6">
         <v>1989</v>
       </c>
       <c r="W6">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF6" t="s">
         <v>59</v>
@@ -1268,7 +1268,7 @@
         <v>0.01</v>
       </c>
       <c r="AO6">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AP6" t="s">
         <v>60</v>
@@ -1297,7 +1297,7 @@
         <v>1989</v>
       </c>
       <c r="G7">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H7" t="s">
         <v>49</v>
@@ -1339,13 +1339,13 @@
         <v>1989</v>
       </c>
       <c r="U7">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V7">
         <v>1989</v>
       </c>
       <c r="W7">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF7" t="s">
         <v>59</v>
@@ -1366,7 +1366,7 @@
         <v>0.01</v>
       </c>
       <c r="AO7">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AP7" t="s">
         <v>60</v>
@@ -1395,7 +1395,7 @@
         <v>1989</v>
       </c>
       <c r="G8">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H8" t="s">
         <v>49</v>
@@ -1437,13 +1437,13 @@
         <v>1989</v>
       </c>
       <c r="U8">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V8">
         <v>1989</v>
       </c>
       <c r="W8">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF8" t="s">
         <v>59</v>
@@ -1464,7 +1464,7 @@
         <v>0.01</v>
       </c>
       <c r="AO8">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AP8" t="s">
         <v>60</v>
@@ -1493,7 +1493,7 @@
         <v>1989</v>
       </c>
       <c r="G9">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H9" t="s">
         <v>49</v>
@@ -1535,13 +1535,13 @@
         <v>1989</v>
       </c>
       <c r="U9">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V9">
         <v>1989</v>
       </c>
       <c r="W9">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF9" t="s">
         <v>59</v>
@@ -1562,7 +1562,7 @@
         <v>0.01</v>
       </c>
       <c r="AO9">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AP9" t="s">
         <v>60</v>
@@ -1591,7 +1591,7 @@
         <v>1989</v>
       </c>
       <c r="G10">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H10" t="s">
         <v>49</v>
@@ -1633,13 +1633,13 @@
         <v>1989</v>
       </c>
       <c r="U10">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V10">
         <v>1989</v>
       </c>
       <c r="W10">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF10" t="s">
         <v>59</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="AN10">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AO10">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="s">
         <v>60</v>
@@ -1689,7 +1689,7 @@
         <v>1989</v>
       </c>
       <c r="G11">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H11" t="s">
         <v>49</v>
@@ -1731,13 +1731,13 @@
         <v>1989</v>
       </c>
       <c r="U11">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V11">
         <v>1989</v>
       </c>
       <c r="W11">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF11" t="s">
         <v>59</v>
@@ -1755,10 +1755,10 @@
         <v>1</v>
       </c>
       <c r="AN11">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AO11">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AP11" t="s">
         <v>60</v>
@@ -1787,7 +1787,7 @@
         <v>1989</v>
       </c>
       <c r="G12">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
@@ -1829,13 +1829,13 @@
         <v>1989</v>
       </c>
       <c r="U12">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V12">
         <v>1989</v>
       </c>
       <c r="W12">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF12" t="s">
         <v>59</v>
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="AN12">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AO12">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="s">
         <v>60</v>
@@ -1885,7 +1885,7 @@
         <v>1989</v>
       </c>
       <c r="G13">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H13" t="s">
         <v>49</v>
@@ -1927,13 +1927,13 @@
         <v>1989</v>
       </c>
       <c r="U13">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V13">
         <v>1989</v>
       </c>
       <c r="W13">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF13" t="s">
         <v>59</v>
@@ -1951,10 +1951,10 @@
         <v>1</v>
       </c>
       <c r="AN13">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AO13">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AP13" t="s">
         <v>60</v>
@@ -1983,7 +1983,7 @@
         <v>1989</v>
       </c>
       <c r="G14">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H14" t="s">
         <v>49</v>
@@ -2025,13 +2025,13 @@
         <v>1989</v>
       </c>
       <c r="U14">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V14">
         <v>1989</v>
       </c>
       <c r="W14">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF14" t="s">
         <v>59</v>
@@ -2081,7 +2081,7 @@
         <v>1989</v>
       </c>
       <c r="G15">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H15" t="s">
         <v>49</v>
@@ -2123,13 +2123,13 @@
         <v>1989</v>
       </c>
       <c r="U15">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V15">
         <v>1989</v>
       </c>
       <c r="W15">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF15" t="s">
         <v>59</v>
@@ -2179,7 +2179,7 @@
         <v>1989</v>
       </c>
       <c r="G16">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H16" t="s">
         <v>49</v>
@@ -2221,13 +2221,13 @@
         <v>1989</v>
       </c>
       <c r="U16">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V16">
         <v>1989</v>
       </c>
       <c r="W16">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF16" t="s">
         <v>59</v>
@@ -2277,7 +2277,7 @@
         <v>1989</v>
       </c>
       <c r="G17">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H17" t="s">
         <v>49</v>
@@ -2319,13 +2319,13 @@
         <v>1989</v>
       </c>
       <c r="U17">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="V17">
         <v>1989</v>
       </c>
       <c r="W17">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF17" t="s">
         <v>59</v>

--- a/Catch models/cinfo_macarellus_cmsy.xlsx
+++ b/Catch models/cinfo_macarellus_cmsy.xlsx
@@ -867,10 +867,10 @@
         <v>0.8</v>
       </c>
       <c r="AI2">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN2">
         <v>0.03</v>
@@ -965,10 +965,10 @@
         <v>0.6</v>
       </c>
       <c r="AI3">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN3">
         <v>0.03</v>
@@ -1063,10 +1063,10 @@
         <v>1</v>
       </c>
       <c r="AI4">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN4">
         <v>0.03</v>
@@ -1161,10 +1161,10 @@
         <v>1.5</v>
       </c>
       <c r="AI5">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN5">
         <v>0.03</v>
@@ -1259,10 +1259,10 @@
         <v>0.8</v>
       </c>
       <c r="AI6">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN6">
         <v>0.01</v>
@@ -1357,10 +1357,10 @@
         <v>0.6</v>
       </c>
       <c r="AI7">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN7">
         <v>0.01</v>
@@ -1455,10 +1455,10 @@
         <v>1</v>
       </c>
       <c r="AI8">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN8">
         <v>0.01</v>
@@ -1553,10 +1553,10 @@
         <v>1.5</v>
       </c>
       <c r="AI9">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN9">
         <v>0.01</v>
@@ -1651,10 +1651,10 @@
         <v>0.8</v>
       </c>
       <c r="AI10">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN10">
         <v>0.01</v>
@@ -1749,10 +1749,10 @@
         <v>0.6</v>
       </c>
       <c r="AI11">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN11">
         <v>0.01</v>
@@ -1847,10 +1847,10 @@
         <v>1</v>
       </c>
       <c r="AI12">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN12">
         <v>0.01</v>
@@ -1945,10 +1945,10 @@
         <v>1.5</v>
       </c>
       <c r="AI13">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN13">
         <v>0.01</v>
@@ -2043,10 +2043,10 @@
         <v>0.8</v>
       </c>
       <c r="AI14">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ14">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN14">
         <v>0.01</v>
@@ -2141,10 +2141,10 @@
         <v>0.6</v>
       </c>
       <c r="AI15">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ15">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN15">
         <v>0.01</v>
@@ -2239,10 +2239,10 @@
         <v>1</v>
       </c>
       <c r="AI16">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ16">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN16">
         <v>0.01</v>
@@ -2337,10 +2337,10 @@
         <v>1.5</v>
       </c>
       <c r="AI17">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AJ17">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AN17">
         <v>0.01</v>

--- a/Catch models/cinfo_macarellus_cmsy.xlsx
+++ b/Catch models/cinfo_macarellus_cmsy.xlsx
@@ -1268,7 +1268,7 @@
         <v>0.01</v>
       </c>
       <c r="AO6">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AP6" t="s">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         <v>0.01</v>
       </c>
       <c r="AO7">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AP7" t="s">
         <v>60</v>
@@ -1464,7 +1464,7 @@
         <v>0.01</v>
       </c>
       <c r="AO8">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AP8" t="s">
         <v>60</v>
@@ -1562,7 +1562,7 @@
         <v>0.01</v>
       </c>
       <c r="AO9">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AP9" t="s">
         <v>60</v>
